--- a/assets/BioMedStatX_Excel_Template.xlsx
+++ b/assets/BioMedStatX_Excel_Template.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="17100" yWindow="720" windowWidth="17120" windowHeight="19900" tabRatio="600" firstSheet="2" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T-Test" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANOVA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repeated T-test" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RM_1F" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TwoWay ANOVA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mixed ANOVA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi-DatasetAnalysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kruskal" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RM_EMM_1F" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANCOVA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="T-Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ANOVA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Repeated T-test" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RM_1F" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TwoWay ANOVA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Mixed ANOVA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Multi-DatasetAnalysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Kruskal" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="RM_EMM_1F" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ANCOVA" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Correlation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Regression (OLS)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Logistic Regression" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -28,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,15 @@
     <font>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -139,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -186,6 +199,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -553,147 +568,983 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>BioMedStatX — how to arrange your data</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="A2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.3</v>
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Golden rule: one row = one observation. Use a single header row, keep labels consistent (WT and wt count as different groups), and do not merge cells.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+      <c r="A4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.3</v>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Which column goes into which mapping bucket:</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.3</v>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Dependent Variable</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>The numeric outcome you measured. Exactly one per analysis.</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WT</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.5</v>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Factor 1</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Your main predictor: a categorical group (t-test / ANOVA) or a continuous variable (correlation / regression).</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.3</v>
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Factor 2</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>A second categorical grouping factor (Two-Way ANOVA, or Mixed ANOVA together with a Subject ID).</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.4</v>
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Subject ID</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Links repeated measurements of the same individual. ALWAYS include it for paired / repeated designs so pairing is by subject, not by row order (re-sorting a subject-less sheet silently mis-pairs).</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.5</v>
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Covariates</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Continuous confounders to adjust for (ANCOVA, or multiple regression).</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.2</v>
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Example sheets in this file:</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.1</v>
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Column -&gt; bucket</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>T-Test</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Independent t-test</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Group -&gt; Factor 1; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>ANOVA</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>One-way ANOVA</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Group -&gt; Factor 1; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Kruskal</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>One-way, nonparametric</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Group -&gt; Factor 1; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Repeated T-test</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Paired t-test</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Subject -&gt; Subject ID; Group -&gt; Factor 1; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>RM_1F</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Repeated-measures ANOVA</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Subject -&gt; Subject ID; Timepoint -&gt; Factor 1; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>RM_EMM_1F</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>RM-ANOVA (vs-baseline post-hoc)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Subject -&gt; Subject ID; Timepoint -&gt; Factor 1; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>TwoWay ANOVA</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Two-way ANOVA</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>FactorA -&gt; Factor 1; FactorB -&gt; Factor 2; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Mixed ANOVA</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Mixed ANOVA</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Subject -&gt; Subject ID; Timepoint &amp; BetweenGrp -&gt; Factor 1 / Factor 2; Value -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>ANCOVA</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Group -&gt; Factor 1; one continuous column -&gt; Covariates; the other -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Pump_time_min -&gt; Factor 1 (continuous); NK_cell_count -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Regression (OLS)</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Linear regression</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Dose_mg -&gt; Factor 1; Baseline -&gt; Covariates; Response -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Logistic regression</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Age &amp; Biomarker -&gt; Factor 1 / Covariates; Responder (0/1) -&gt; Dependent Variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Multi-DatasetAnalysis</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Multiple datasets (wide format)</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Each measurement column is analysed across the sample groups</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Timepoint</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>22.86</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26.42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25.76</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>27.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24.81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>18.92</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>22.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25.64</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>28.78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30.54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>22.79</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>23.48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24.56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>29.65</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>23.54</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16.11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>18.59</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>19.51</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>27.82</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>22.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>25.83</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>26.47</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>27.58</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>22.03</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>48h</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>19.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1192,7 +2043,935 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Pump_time_min</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>NK_cell_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="n">
+        <v>91</v>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="n">
+        <v>135</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>135</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>71</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>82</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>123</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>81</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>95</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>115</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>94</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>73</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>119</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n">
+        <v>53</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>780</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Dose_mg</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>106.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>131.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>111</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>107.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>117</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>137.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>92.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>117.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>112.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>114</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>133.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>152.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>107.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Biomarker</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Responder</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B2" s="19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="n">
+        <v>69</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>74</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>71</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>53</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n">
+        <v>79</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="n">
+        <v>53</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="n">
+        <v>76</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1942,124 +3721,179 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="19" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="19" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="19" t="n">
         <v>78</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="19" t="n">
         <v>83</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="19" t="n">
         <v>91</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="19" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="19" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="19" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="19" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="19" t="n">
         <v>88</v>
       </c>
     </row>
@@ -2069,7 +3903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2505,7 +4339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3352,7 +5186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4207,7 +6041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4634,7 +6468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5178,635 +7012,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Timepoint</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>22.86</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24.66</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>26.42</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>23.17</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>25.76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>27.36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>18.92</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>23.66</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>22.38</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>25.64</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S04</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>28.78</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>S04</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>30.54</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S04</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>27.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>22.79</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>26.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>27.9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>23.48</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>24.56</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>25.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>29.65</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>23.54</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>S07</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16.11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S07</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>18.59</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S07</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S07</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>19.51</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S08</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>21.55</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S08</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>24.2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>S08</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>27.82</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>S08</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>22.25</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>22.03</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>25.83</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>26.47</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>27.58</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>20.75</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>24h</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>22.03</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>48h</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>19.01</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>